--- a/artfynd/A 30368-2024 artfynd.xlsx
+++ b/artfynd/A 30368-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62391934</v>
+        <v>97541537</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,20 +703,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedsåsbodarna 200 m Ö om fäb., Dlr</t>
+          <t>Hedsåsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509187.1736400062</v>
+        <v>509262</v>
       </c>
       <c r="R2" t="n">
-        <v>6748223.314716681</v>
+        <v>6748240</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Dalafloran [82]   t.rikl.</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,39 +771,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>lövlund</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Inge Palmqvist</t>
+          <t>Marianne Pasanen-Mortensen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Ljung, Lennart Bratt</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Dalaflorans databas</t>
-        </is>
-      </c>
+          <t>Marianne Pasanen-Mortensen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>97541538</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509210.6915629954</v>
+        <v>509211</v>
       </c>
       <c r="R3" t="n">
-        <v>6748184.408594684</v>
+        <v>6748185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,19 +868,9 @@
           <t>2021-08-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,150 +894,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>97541652</v>
-      </c>
-      <c r="B4" t="n">
-        <v>40972</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100453</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Trolldruvemätare</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Baptria tibiale</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Esper, 1790)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Hedsåsbodarna, Dlr</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>509210.6915629954</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6748184.408594684</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Rättvik</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Rättvik</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Larver eftersökta på samtliga 203 plantor av svart trolldruva.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Bergstopp med bra solinstrålning.</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Marianne Pasanen-Mortensen</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Marianne Pasanen-Mortensen</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trolldruvemätare (nationellt)</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30368-2024 artfynd.xlsx
+++ b/artfynd/A 30368-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97541537</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97541538</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>